--- a/artfynd/A 30483-2024 artfynd.xlsx
+++ b/artfynd/A 30483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103995873</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551770.5006389725</v>
+        <v>551771</v>
       </c>
       <c r="R2" t="n">
-        <v>7016778.96926375</v>
+        <v>7016779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103995823</v>
+        <v>103995862</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551770.5006389725</v>
+        <v>551768</v>
       </c>
       <c r="R3" t="n">
-        <v>7016778.96926375</v>
+        <v>7016780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103995862</v>
+        <v>103995823</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551767.3242159043</v>
+        <v>551771</v>
       </c>
       <c r="R4" t="n">
-        <v>7016780.268689417</v>
+        <v>7016779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,16 +1026,11 @@
         <v>107659407</v>
       </c>
       <c r="B5" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1088,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551679.1489777844</v>
+        <v>551679</v>
       </c>
       <c r="R5" t="n">
-        <v>7016741.036579535</v>
+        <v>7016741</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1157,6 +1137,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103401908</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>551818</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7016847</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30483-2024 artfynd.xlsx
+++ b/artfynd/A 30483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995862</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995823</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107659407</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,8 +1259,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>